--- a/upload/pagamentos2026.xlsx
+++ b/upload/pagamentos2026.xlsx
@@ -9,17 +9,20 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11100"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="2" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$Y$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="257">
   <si>
     <t>ano</t>
   </si>
@@ -706,6 +709,90 @@
   </si>
   <si>
     <t>NÃO</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>MATERIAL DE CONSUMO</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>COMBUSTIVEIS E LUBRIFICANTES PARA VEICULOS AUTOMOTORES</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>VIBRA ENERGIA S.A</t>
+  </si>
+  <si>
+    <t>34.274.233/0025-71</t>
+  </si>
+  <si>
+    <t>16/06/2026</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>19/06/2026</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>17/06/2026</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>244</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>245</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>248</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>22/06/2026</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
+  </si>
+  <si>
+    <t>254</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1155,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -1171,10 +1258,10 @@
         <v>91</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J2" t="s">
         <v>27</v>
@@ -1183,40 +1270,43 @@
         <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="M2" t="s">
         <v>54</v>
       </c>
       <c r="N2" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="O2" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="P2" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="Q2" t="s">
         <v>30</v>
       </c>
       <c r="R2">
-        <v>712.06</v>
+        <v>126.84</v>
       </c>
       <c r="S2" t="s">
-        <v>122</v>
+        <v>165</v>
       </c>
       <c r="T2" t="s">
         <v>77</v>
       </c>
       <c r="U2" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="V2">
-        <v>677.88</v>
+        <v>126.84</v>
       </c>
       <c r="W2" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
@@ -1233,7 +1323,7 @@
         <v>202</v>
       </c>
       <c r="E3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F3" t="s">
         <v>90</v>
@@ -1254,7 +1344,7 @@
         <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M3" t="s">
         <v>54</v>
@@ -1266,16 +1356,16 @@
         <v>97</v>
       </c>
       <c r="P3" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="Q3" t="s">
         <v>30</v>
       </c>
       <c r="R3">
-        <v>126.84</v>
+        <v>22827.24</v>
       </c>
       <c r="S3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="T3" t="s">
         <v>77</v>
@@ -1284,13 +1374,13 @@
         <v>127</v>
       </c>
       <c r="V3">
-        <v>126.84</v>
+        <v>22827.24</v>
       </c>
       <c r="W3" t="s">
         <v>214</v>
       </c>
       <c r="X3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
@@ -1307,7 +1397,7 @@
         <v>202</v>
       </c>
       <c r="E4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F4" t="s">
         <v>90</v>
@@ -1328,7 +1418,7 @@
         <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
         <v>54</v>
@@ -1340,31 +1430,31 @@
         <v>97</v>
       </c>
       <c r="P4" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
         <v>30</v>
       </c>
       <c r="R4">
-        <v>22827.24</v>
+        <v>3397</v>
       </c>
       <c r="S4" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="T4" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="U4" t="s">
         <v>127</v>
       </c>
       <c r="V4">
-        <v>22827.24</v>
+        <v>3397</v>
       </c>
       <c r="W4" t="s">
         <v>214</v>
       </c>
       <c r="X4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
@@ -1381,7 +1471,7 @@
         <v>202</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F5" t="s">
         <v>90</v>
@@ -1402,7 +1492,7 @@
         <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>159</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
         <v>54</v>
@@ -1414,31 +1504,31 @@
         <v>97</v>
       </c>
       <c r="P5" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="R5">
-        <v>5062</v>
+        <v>320</v>
       </c>
       <c r="S5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="T5" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="U5" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="V5">
-        <v>5062</v>
+        <v>320</v>
       </c>
       <c r="W5" t="s">
         <v>214</v>
       </c>
       <c r="X5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -1455,19 +1545,19 @@
         <v>202</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J6" t="s">
         <v>27</v>
@@ -1476,40 +1566,43 @@
         <v>28</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>182</v>
       </c>
       <c r="M6" t="s">
         <v>54</v>
       </c>
       <c r="N6" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="O6" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="P6" t="s">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R6">
-        <v>63493.65</v>
+        <v>1225</v>
       </c>
       <c r="S6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="T6" t="s">
         <v>125</v>
       </c>
       <c r="U6" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="V6">
-        <v>44279.05</v>
+        <v>1225</v>
       </c>
       <c r="W6" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X6" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
@@ -1526,7 +1619,7 @@
         <v>202</v>
       </c>
       <c r="E7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F7" t="s">
         <v>90</v>
@@ -1547,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>159</v>
       </c>
       <c r="M7" t="s">
         <v>54</v>
@@ -1559,31 +1652,31 @@
         <v>97</v>
       </c>
       <c r="P7" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="Q7" t="s">
         <v>30</v>
       </c>
       <c r="R7">
-        <v>3397</v>
+        <v>5062</v>
       </c>
       <c r="S7" t="s">
-        <v>181</v>
+        <v>121</v>
       </c>
       <c r="T7" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="V7">
-        <v>3397</v>
+        <v>5062</v>
       </c>
       <c r="W7" t="s">
         <v>214</v>
       </c>
       <c r="X7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
@@ -1600,19 +1693,19 @@
         <v>202</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
         <v>27</v>
@@ -1621,43 +1714,40 @@
         <v>28</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M8" t="s">
         <v>54</v>
       </c>
       <c r="N8" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="O8" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="P8" t="s">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="Q8" t="s">
         <v>34</v>
       </c>
       <c r="R8">
-        <v>320</v>
+        <v>63493.65</v>
       </c>
       <c r="S8" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="T8" t="s">
         <v>125</v>
       </c>
       <c r="U8" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="V8">
-        <v>320</v>
+        <v>44279.05</v>
       </c>
       <c r="W8" t="s">
-        <v>214</v>
-      </c>
-      <c r="X8" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
@@ -1674,7 +1764,7 @@
         <v>202</v>
       </c>
       <c r="E9" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F9" t="s">
         <v>90</v>
@@ -1683,10 +1773,10 @@
         <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J9" t="s">
         <v>27</v>
@@ -1695,43 +1785,40 @@
         <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="M9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N9" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="O9" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="P9" t="s">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="Q9" t="s">
         <v>30</v>
       </c>
       <c r="R9">
-        <v>1225</v>
+        <v>6012.64</v>
       </c>
       <c r="S9" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="T9" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="U9" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="V9">
-        <v>1225</v>
+        <v>5724.03</v>
       </c>
       <c r="W9" t="s">
-        <v>214</v>
-      </c>
-      <c r="X9" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
@@ -1748,7 +1835,7 @@
         <v>202</v>
       </c>
       <c r="E10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F10" t="s">
         <v>90</v>
@@ -1769,10 +1856,10 @@
         <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="M10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N10" t="s">
         <v>137</v>
@@ -1781,25 +1868,25 @@
         <v>138</v>
       </c>
       <c r="P10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="Q10" t="s">
         <v>30</v>
       </c>
       <c r="R10">
-        <v>6012.64</v>
+        <v>712.06</v>
       </c>
       <c r="S10" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="U10" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="V10">
-        <v>5724.03</v>
+        <v>677.88</v>
       </c>
       <c r="W10" t="s">
         <v>228</v>
@@ -2041,7 +2128,7 @@
         <v>202</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F14" t="s">
         <v>90</v>
@@ -2062,7 +2149,7 @@
         <v>28</v>
       </c>
       <c r="L14" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="M14" t="s">
         <v>54</v>
@@ -2080,25 +2167,25 @@
         <v>30</v>
       </c>
       <c r="R14">
-        <v>5600</v>
+        <v>416</v>
       </c>
       <c r="S14" t="s">
-        <v>89</v>
+        <v>154</v>
       </c>
       <c r="T14" t="s">
         <v>57</v>
       </c>
       <c r="U14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="V14">
-        <v>5600</v>
+        <v>416</v>
       </c>
       <c r="W14" t="s">
         <v>214</v>
       </c>
       <c r="X14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
@@ -2115,7 +2202,7 @@
         <v>202</v>
       </c>
       <c r="E15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F15" t="s">
         <v>90</v>
@@ -2136,7 +2223,7 @@
         <v>28</v>
       </c>
       <c r="L15" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="M15" t="s">
         <v>54</v>
@@ -2154,10 +2241,10 @@
         <v>30</v>
       </c>
       <c r="R15">
-        <v>416</v>
+        <v>596</v>
       </c>
       <c r="S15" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="T15" t="s">
         <v>57</v>
@@ -2166,7 +2253,7 @@
         <v>31</v>
       </c>
       <c r="V15">
-        <v>416</v>
+        <v>596</v>
       </c>
       <c r="W15" t="s">
         <v>214</v>
@@ -2189,7 +2276,7 @@
         <v>202</v>
       </c>
       <c r="E16" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F16" t="s">
         <v>90</v>
@@ -2210,7 +2297,7 @@
         <v>28</v>
       </c>
       <c r="L16" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="M16" t="s">
         <v>54</v>
@@ -2228,25 +2315,25 @@
         <v>30</v>
       </c>
       <c r="R16">
-        <v>596</v>
+        <v>5600</v>
       </c>
       <c r="S16" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="T16" t="s">
         <v>57</v>
       </c>
       <c r="U16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V16">
-        <v>596</v>
+        <v>5600</v>
       </c>
       <c r="W16" t="s">
         <v>214</v>
       </c>
       <c r="X16" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.25">
@@ -2482,7 +2569,7 @@
         <v>202</v>
       </c>
       <c r="E20" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F20" t="s">
         <v>90</v>
@@ -2491,10 +2578,10 @@
         <v>91</v>
       </c>
       <c r="H20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I20" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J20" t="s">
         <v>27</v>
@@ -2503,43 +2590,40 @@
         <v>28</v>
       </c>
       <c r="L20" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="M20" t="s">
         <v>54</v>
       </c>
       <c r="N20" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="O20" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="P20" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="Q20" t="s">
         <v>34</v>
       </c>
       <c r="R20">
-        <v>712.06</v>
+        <v>1225</v>
       </c>
       <c r="S20" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="T20" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="U20" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="V20">
-        <v>677.88</v>
+        <v>1225</v>
       </c>
       <c r="W20" t="s">
-        <v>214</v>
-      </c>
-      <c r="X20" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.25">
@@ -2556,7 +2640,7 @@
         <v>202</v>
       </c>
       <c r="E21" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F21" t="s">
         <v>90</v>
@@ -2565,10 +2649,10 @@
         <v>91</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J21" t="s">
         <v>27</v>
@@ -2577,37 +2661,37 @@
         <v>28</v>
       </c>
       <c r="L21" t="s">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="M21" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N21" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="O21" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="P21" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="Q21" t="s">
         <v>34</v>
       </c>
       <c r="R21">
-        <v>6012.64</v>
+        <v>596</v>
       </c>
       <c r="S21" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="T21" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="U21" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="V21">
-        <v>5724.03</v>
+        <v>596</v>
       </c>
       <c r="W21" t="s">
         <v>228</v>
@@ -2627,19 +2711,19 @@
         <v>202</v>
       </c>
       <c r="E22" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="F22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J22" t="s">
         <v>27</v>
@@ -2648,43 +2732,40 @@
         <v>28</v>
       </c>
       <c r="L22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="M22" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="N22" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="O22" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P22" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="Q22" t="s">
         <v>34</v>
       </c>
       <c r="R22">
-        <v>3728.76</v>
+        <v>5600</v>
       </c>
       <c r="S22" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="T22" t="s">
-        <v>58</v>
+        <v>105</v>
       </c>
       <c r="U22" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="V22">
-        <v>3728.76</v>
+        <v>5600</v>
       </c>
       <c r="W22" t="s">
-        <v>214</v>
-      </c>
-      <c r="X22" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.25">
@@ -2701,7 +2782,7 @@
         <v>202</v>
       </c>
       <c r="E23" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F23" t="s">
         <v>90</v>
@@ -2722,7 +2803,7 @@
         <v>28</v>
       </c>
       <c r="L23" t="s">
-        <v>182</v>
+        <v>66</v>
       </c>
       <c r="M23" t="s">
         <v>54</v>
@@ -2740,10 +2821,10 @@
         <v>34</v>
       </c>
       <c r="R23">
-        <v>1225</v>
+        <v>416</v>
       </c>
       <c r="S23" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="T23" t="s">
         <v>105</v>
@@ -2752,7 +2833,7 @@
         <v>109</v>
       </c>
       <c r="V23">
-        <v>1225</v>
+        <v>416</v>
       </c>
       <c r="W23" t="s">
         <v>228</v>
@@ -2772,7 +2853,7 @@
         <v>202</v>
       </c>
       <c r="E24" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F24" t="s">
         <v>90</v>
@@ -2793,7 +2874,7 @@
         <v>28</v>
       </c>
       <c r="L24" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="M24" t="s">
         <v>54</v>
@@ -2811,10 +2892,10 @@
         <v>34</v>
       </c>
       <c r="R24">
-        <v>596</v>
+        <v>776</v>
       </c>
       <c r="S24" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="T24" t="s">
         <v>105</v>
@@ -2823,7 +2904,7 @@
         <v>109</v>
       </c>
       <c r="V24">
-        <v>596</v>
+        <v>776</v>
       </c>
       <c r="W24" t="s">
         <v>228</v>
@@ -2843,7 +2924,7 @@
         <v>202</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="F25" t="s">
         <v>90</v>
@@ -2864,7 +2945,7 @@
         <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="M25" t="s">
         <v>54</v>
@@ -2882,10 +2963,10 @@
         <v>34</v>
       </c>
       <c r="R25">
-        <v>5600</v>
+        <v>416</v>
       </c>
       <c r="S25" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="T25" t="s">
         <v>105</v>
@@ -2894,7 +2975,7 @@
         <v>109</v>
       </c>
       <c r="V25">
-        <v>5600</v>
+        <v>416</v>
       </c>
       <c r="W25" t="s">
         <v>228</v>
@@ -2914,7 +2995,7 @@
         <v>202</v>
       </c>
       <c r="E26" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F26" t="s">
         <v>90</v>
@@ -2935,7 +3016,7 @@
         <v>28</v>
       </c>
       <c r="L26" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
         <v>54</v>
@@ -2950,13 +3031,13 @@
         <v>61</v>
       </c>
       <c r="Q26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R26">
-        <v>416</v>
+        <v>320</v>
       </c>
       <c r="S26" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="T26" t="s">
         <v>105</v>
@@ -2965,7 +3046,7 @@
         <v>109</v>
       </c>
       <c r="V26">
-        <v>416</v>
+        <v>320</v>
       </c>
       <c r="W26" t="s">
         <v>228</v>
@@ -2985,7 +3066,7 @@
         <v>202</v>
       </c>
       <c r="E27" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F27" t="s">
         <v>90</v>
@@ -3006,7 +3087,7 @@
         <v>28</v>
       </c>
       <c r="L27" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
         <v>54</v>
@@ -3021,13 +3102,13 @@
         <v>61</v>
       </c>
       <c r="Q27" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="R27">
-        <v>776</v>
+        <v>3397</v>
       </c>
       <c r="S27" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="T27" t="s">
         <v>105</v>
@@ -3036,7 +3117,7 @@
         <v>109</v>
       </c>
       <c r="V27">
-        <v>776</v>
+        <v>3397</v>
       </c>
       <c r="W27" t="s">
         <v>228</v>
@@ -3056,7 +3137,7 @@
         <v>202</v>
       </c>
       <c r="E28" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F28" t="s">
         <v>90</v>
@@ -3071,16 +3152,16 @@
         <v>95</v>
       </c>
       <c r="J28" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="K28" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="L28" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="M28" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="N28" t="s">
         <v>96</v>
@@ -3095,25 +3176,22 @@
         <v>34</v>
       </c>
       <c r="R28">
-        <v>956</v>
+        <v>2328</v>
       </c>
       <c r="S28" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="T28" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="U28" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="V28">
-        <v>956</v>
+        <v>2328</v>
       </c>
       <c r="W28" t="s">
-        <v>214</v>
-      </c>
-      <c r="X28" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.25">
@@ -3130,7 +3208,7 @@
         <v>202</v>
       </c>
       <c r="E29" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="F29" t="s">
         <v>90</v>
@@ -3151,7 +3229,7 @@
         <v>28</v>
       </c>
       <c r="L29" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="M29" t="s">
         <v>54</v>
@@ -3169,22 +3247,25 @@
         <v>34</v>
       </c>
       <c r="R29">
-        <v>416</v>
+        <v>956</v>
       </c>
       <c r="S29" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="T29" t="s">
         <v>105</v>
       </c>
       <c r="U29" t="s">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="V29">
-        <v>416</v>
+        <v>956</v>
       </c>
       <c r="W29" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X29" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.25">
@@ -3272,7 +3353,7 @@
         <v>202</v>
       </c>
       <c r="E31" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F31" t="s">
         <v>90</v>
@@ -3281,10 +3362,10 @@
         <v>91</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J31" t="s">
         <v>27</v>
@@ -3293,40 +3374,43 @@
         <v>28</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="M31" t="s">
         <v>54</v>
       </c>
       <c r="N31" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="O31" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="P31" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="Q31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R31">
-        <v>320</v>
+        <v>712.06</v>
       </c>
       <c r="S31" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="U31" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="V31">
-        <v>320</v>
+        <v>677.88</v>
       </c>
       <c r="W31" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X31" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.25">
@@ -3343,7 +3427,7 @@
         <v>202</v>
       </c>
       <c r="E32" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F32" t="s">
         <v>90</v>
@@ -3352,10 +3436,10 @@
         <v>91</v>
       </c>
       <c r="H32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I32" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J32" t="s">
         <v>27</v>
@@ -3364,37 +3448,37 @@
         <v>28</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="M32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N32" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="O32" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="P32" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
       <c r="Q32" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R32">
-        <v>3397</v>
+        <v>6012.64</v>
       </c>
       <c r="S32" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="T32" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
       <c r="U32" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="V32">
-        <v>3397</v>
+        <v>5724.03</v>
       </c>
       <c r="W32" t="s">
         <v>228</v>
@@ -3414,61 +3498,64 @@
         <v>202</v>
       </c>
       <c r="E33" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="I33" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="J33" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="K33" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="M33" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="N33" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="O33" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="P33" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="Q33" t="s">
         <v>34</v>
       </c>
       <c r="R33">
-        <v>2328</v>
+        <v>3728.76</v>
       </c>
       <c r="S33" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="T33" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="U33" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="V33">
-        <v>2328</v>
+        <v>3728.76</v>
       </c>
       <c r="W33" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X33" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.25">
@@ -3485,7 +3572,7 @@
         <v>202</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F34" t="s">
         <v>90</v>
@@ -3506,40 +3593,43 @@
         <v>28</v>
       </c>
       <c r="L34" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="M34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>211</v>
       </c>
       <c r="O34" t="s">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="P34" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="Q34" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R34">
-        <v>6012.64</v>
+        <v>85781.23</v>
       </c>
       <c r="S34" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="T34" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="U34" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="V34">
-        <v>5724.03</v>
+        <v>85781.23</v>
       </c>
       <c r="W34" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X34" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.25">
@@ -3556,19 +3646,19 @@
         <v>202</v>
       </c>
       <c r="E35" t="s">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="F35" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="I35" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J35" t="s">
         <v>27</v>
@@ -3577,40 +3667,43 @@
         <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="M35" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="N35" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="O35" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P35" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="Q35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R35">
-        <v>3894.37</v>
+        <v>22827.24</v>
       </c>
       <c r="S35" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="T35" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="U35" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="V35">
-        <v>3894.37</v>
+        <v>22827.24</v>
       </c>
       <c r="W35" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X35" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.25">
@@ -3627,19 +3720,19 @@
         <v>202</v>
       </c>
       <c r="E36" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="F36" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G36" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H36" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="I36" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J36" t="s">
         <v>27</v>
@@ -3648,40 +3741,43 @@
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>30</v>
+        <v>159</v>
       </c>
       <c r="M36" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="N36" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="O36" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P36" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="Q36" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R36">
-        <v>160.09</v>
+        <v>5062</v>
       </c>
       <c r="S36" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="T36" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
       <c r="U36" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="V36">
-        <v>160.09</v>
+        <v>5062</v>
       </c>
       <c r="W36" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X36" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.25">
@@ -3698,64 +3794,61 @@
         <v>202</v>
       </c>
       <c r="E37" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="F37" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G37" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H37" t="s">
+        <v>39</v>
+      </c>
+      <c r="I37" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" t="s">
+        <v>28</v>
+      </c>
+      <c r="L37" t="s">
         <v>34</v>
       </c>
-      <c r="I37" t="s">
-        <v>92</v>
-      </c>
-      <c r="J37" t="s">
-        <v>27</v>
-      </c>
-      <c r="K37" t="s">
-        <v>28</v>
-      </c>
-      <c r="L37" t="s">
-        <v>164</v>
-      </c>
       <c r="M37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N37" t="s">
-        <v>211</v>
+        <v>74</v>
       </c>
       <c r="O37" t="s">
-        <v>212</v>
+        <v>75</v>
       </c>
       <c r="P37" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="Q37" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R37">
-        <v>85781.23</v>
+        <v>51923.16</v>
       </c>
       <c r="S37" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="T37" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="U37" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="V37">
-        <v>85781.23</v>
+        <v>42894.92</v>
       </c>
       <c r="W37" t="s">
-        <v>214</v>
-      </c>
-      <c r="X37" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.25">
@@ -3781,10 +3874,10 @@
         <v>91</v>
       </c>
       <c r="H38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J38" t="s">
         <v>27</v>
@@ -3793,43 +3886,40 @@
         <v>28</v>
       </c>
       <c r="L38" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="M38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N38" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="O38" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="P38" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="Q38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R38">
-        <v>22827.24</v>
+        <v>6012.64</v>
       </c>
       <c r="S38" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="T38" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="U38" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="V38">
-        <v>22827.24</v>
+        <v>5724.03</v>
       </c>
       <c r="W38" t="s">
-        <v>214</v>
-      </c>
-      <c r="X38" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.25">
@@ -3846,19 +3936,19 @@
         <v>202</v>
       </c>
       <c r="E39" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="F39" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="I39" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="J39" t="s">
         <v>27</v>
@@ -3867,43 +3957,40 @@
         <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>159</v>
+        <v>30</v>
       </c>
       <c r="M39" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="N39" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="O39" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="P39" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="Q39" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R39">
-        <v>5062</v>
+        <v>3894.37</v>
       </c>
       <c r="S39" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="T39" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="U39" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="V39">
-        <v>5062</v>
+        <v>3894.37</v>
       </c>
       <c r="W39" t="s">
-        <v>214</v>
-      </c>
-      <c r="X39" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.25">
@@ -3923,55 +4010,55 @@
         <v>166</v>
       </c>
       <c r="F40" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s">
+        <v>102</v>
+      </c>
+      <c r="I40" t="s">
+        <v>103</v>
+      </c>
+      <c r="J40" t="s">
+        <v>27</v>
+      </c>
+      <c r="K40" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" t="s">
+        <v>30</v>
+      </c>
+      <c r="M40" t="s">
+        <v>29</v>
+      </c>
+      <c r="N40" t="s">
+        <v>114</v>
+      </c>
+      <c r="O40" t="s">
+        <v>115</v>
+      </c>
+      <c r="P40" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q40" t="s">
         <v>39</v>
       </c>
-      <c r="I40" t="s">
-        <v>80</v>
-      </c>
-      <c r="J40" t="s">
-        <v>27</v>
-      </c>
-      <c r="K40" t="s">
-        <v>28</v>
-      </c>
-      <c r="L40" t="s">
-        <v>34</v>
-      </c>
-      <c r="M40" t="s">
-        <v>54</v>
-      </c>
-      <c r="N40" t="s">
-        <v>74</v>
-      </c>
-      <c r="O40" t="s">
-        <v>75</v>
-      </c>
-      <c r="P40" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>35</v>
-      </c>
       <c r="R40">
-        <v>51923.16</v>
+        <v>160.09</v>
       </c>
       <c r="S40" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="T40" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="U40" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="V40">
-        <v>42894.92</v>
+        <v>160.09</v>
       </c>
       <c r="W40" t="s">
         <v>228</v>
@@ -4062,7 +4149,7 @@
         <v>202</v>
       </c>
       <c r="E42" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="F42" t="s">
         <v>90</v>
@@ -4071,10 +4158,10 @@
         <v>91</v>
       </c>
       <c r="H42" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J42" t="s">
         <v>27</v>
@@ -4083,43 +4170,43 @@
         <v>28</v>
       </c>
       <c r="L42" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="M42" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N42" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O42" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P42" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="Q42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R42">
-        <v>55</v>
+        <v>416</v>
       </c>
       <c r="S42" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="T42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="U42" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="V42">
-        <v>55</v>
+        <v>416</v>
       </c>
       <c r="W42" t="s">
         <v>214</v>
       </c>
       <c r="X42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.25">
@@ -4136,7 +4223,7 @@
         <v>202</v>
       </c>
       <c r="E43" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="F43" t="s">
         <v>90</v>
@@ -4145,10 +4232,10 @@
         <v>91</v>
       </c>
       <c r="H43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I43" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J43" t="s">
         <v>27</v>
@@ -4157,43 +4244,43 @@
         <v>28</v>
       </c>
       <c r="L43" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="M43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N43" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="O43" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P43" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q43" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R43">
-        <v>22827.24</v>
+        <v>55</v>
       </c>
       <c r="S43" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="T43" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="U43" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="V43">
-        <v>22827.24</v>
+        <v>55</v>
       </c>
       <c r="W43" t="s">
         <v>214</v>
       </c>
       <c r="X43" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.25">
@@ -4432,7 +4519,7 @@
         <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="F47" t="s">
         <v>90</v>
@@ -4453,7 +4540,7 @@
         <v>28</v>
       </c>
       <c r="L47" t="s">
-        <v>159</v>
+        <v>39</v>
       </c>
       <c r="M47" t="s">
         <v>54</v>
@@ -4465,25 +4552,25 @@
         <v>97</v>
       </c>
       <c r="P47" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q47" t="s">
         <v>35</v>
       </c>
       <c r="R47">
-        <v>5062</v>
+        <v>416</v>
       </c>
       <c r="S47" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="T47" t="s">
         <v>40</v>
       </c>
       <c r="U47" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="V47">
-        <v>5062</v>
+        <v>416</v>
       </c>
       <c r="W47" t="s">
         <v>214</v>
@@ -4506,7 +4593,7 @@
         <v>202</v>
       </c>
       <c r="E48" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="F48" t="s">
         <v>90</v>
@@ -4527,7 +4614,7 @@
         <v>28</v>
       </c>
       <c r="L48" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="M48" t="s">
         <v>54</v>
@@ -4545,10 +4632,10 @@
         <v>35</v>
       </c>
       <c r="R48">
-        <v>416</v>
+        <v>596</v>
       </c>
       <c r="S48" t="s">
-        <v>187</v>
+        <v>145</v>
       </c>
       <c r="T48" t="s">
         <v>40</v>
@@ -4557,7 +4644,7 @@
         <v>87</v>
       </c>
       <c r="V48">
-        <v>416</v>
+        <v>596</v>
       </c>
       <c r="W48" t="s">
         <v>214</v>
@@ -4580,7 +4667,7 @@
         <v>202</v>
       </c>
       <c r="E49" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F49" t="s">
         <v>90</v>
@@ -4601,7 +4688,7 @@
         <v>28</v>
       </c>
       <c r="L49" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
       <c r="M49" t="s">
         <v>54</v>
@@ -4613,25 +4700,25 @@
         <v>97</v>
       </c>
       <c r="P49" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="Q49" t="s">
         <v>35</v>
       </c>
       <c r="R49">
-        <v>596</v>
+        <v>22827.24</v>
       </c>
       <c r="S49" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="T49" t="s">
         <v>40</v>
       </c>
       <c r="U49" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="V49">
-        <v>596</v>
+        <v>22827.24</v>
       </c>
       <c r="W49" t="s">
         <v>214</v>
@@ -4654,7 +4741,7 @@
         <v>202</v>
       </c>
       <c r="E50" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F50" t="s">
         <v>90</v>
@@ -4675,7 +4762,7 @@
         <v>28</v>
       </c>
       <c r="L50" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M50" t="s">
         <v>54</v>
@@ -4693,19 +4780,19 @@
         <v>35</v>
       </c>
       <c r="R50">
-        <v>416</v>
+        <v>1732</v>
       </c>
       <c r="S50" t="s">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="T50" t="s">
         <v>40</v>
       </c>
       <c r="U50" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="V50">
-        <v>416</v>
+        <v>1732</v>
       </c>
       <c r="W50" t="s">
         <v>214</v>
@@ -4728,19 +4815,19 @@
         <v>202</v>
       </c>
       <c r="E51" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="F51" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G51" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="H51" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I51" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J51" t="s">
         <v>27</v>
@@ -4749,43 +4836,40 @@
         <v>28</v>
       </c>
       <c r="L51" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="M51" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="N51" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="O51" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="P51" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q51" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R51">
-        <v>127.56</v>
+        <v>58454.8</v>
       </c>
       <c r="S51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="T51" t="s">
         <v>40</v>
       </c>
       <c r="U51" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="V51">
-        <v>127.56</v>
+        <v>48438.77</v>
       </c>
       <c r="W51" t="s">
-        <v>214</v>
-      </c>
-      <c r="X51" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.25">
@@ -4802,7 +4886,7 @@
         <v>202</v>
       </c>
       <c r="E52" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F52" t="s">
         <v>90</v>
@@ -4823,7 +4907,7 @@
         <v>28</v>
       </c>
       <c r="L52" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="M52" t="s">
         <v>54</v>
@@ -4835,25 +4919,25 @@
         <v>97</v>
       </c>
       <c r="P52" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="Q52" t="s">
         <v>35</v>
       </c>
       <c r="R52">
-        <v>1732</v>
+        <v>5062</v>
       </c>
       <c r="S52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="T52" t="s">
         <v>40</v>
       </c>
       <c r="U52" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="V52">
-        <v>1732</v>
+        <v>5062</v>
       </c>
       <c r="W52" t="s">
         <v>214</v>
@@ -4876,7 +4960,7 @@
         <v>202</v>
       </c>
       <c r="E53" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F53" t="s">
         <v>90</v>
@@ -4897,7 +4981,7 @@
         <v>28</v>
       </c>
       <c r="L53" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="M53" t="s">
         <v>54</v>
@@ -4909,16 +4993,16 @@
         <v>97</v>
       </c>
       <c r="P53" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="Q53" t="s">
         <v>35</v>
       </c>
       <c r="R53">
-        <v>4644</v>
+        <v>127.56</v>
       </c>
       <c r="S53" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="T53" t="s">
         <v>40</v>
@@ -4927,7 +5011,7 @@
         <v>70</v>
       </c>
       <c r="V53">
-        <v>4644</v>
+        <v>127.56</v>
       </c>
       <c r="W53" t="s">
         <v>214</v>
@@ -4950,7 +5034,7 @@
         <v>202</v>
       </c>
       <c r="E54" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="F54" t="s">
         <v>90</v>
@@ -4959,10 +5043,10 @@
         <v>91</v>
       </c>
       <c r="H54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J54" t="s">
         <v>27</v>
@@ -4971,40 +5055,43 @@
         <v>28</v>
       </c>
       <c r="L54" t="s">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="M54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N54" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O54" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="P54" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="Q54" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R54">
-        <v>165</v>
+        <v>4644</v>
       </c>
       <c r="S54" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T54" t="s">
         <v>40</v>
       </c>
       <c r="U54" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="V54">
-        <v>165</v>
+        <v>4644</v>
       </c>
       <c r="W54" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X54" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.25">
@@ -5021,19 +5108,19 @@
         <v>202</v>
       </c>
       <c r="E55" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="F55" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H55" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s">
         <v>27</v>
@@ -5042,40 +5129,43 @@
         <v>28</v>
       </c>
       <c r="L55" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="M55" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="N55" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="O55" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="P55" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="Q55" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R55">
-        <v>58454.8</v>
+        <v>956</v>
       </c>
       <c r="S55" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="T55" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="U55" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="V55">
-        <v>48438.77</v>
+        <v>956</v>
       </c>
       <c r="W55" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X55" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.25">
@@ -5092,7 +5182,7 @@
         <v>202</v>
       </c>
       <c r="E56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F56" t="s">
         <v>90</v>
@@ -5101,52 +5191,55 @@
         <v>91</v>
       </c>
       <c r="H56" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="K56" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="L56" t="s">
-        <v>179</v>
+        <v>89</v>
       </c>
       <c r="M56" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="N56" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="O56" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="P56" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="Q56" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="R56">
-        <v>6012.64</v>
+        <v>2328</v>
       </c>
       <c r="S56" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="T56" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="U56" t="s">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="V56">
-        <v>5724.03</v>
+        <v>2328</v>
       </c>
       <c r="W56" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X56" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.25">
@@ -5163,7 +5256,7 @@
         <v>202</v>
       </c>
       <c r="E57" t="s">
-        <v>207</v>
+        <v>166</v>
       </c>
       <c r="F57" t="s">
         <v>90</v>
@@ -5184,37 +5277,37 @@
         <v>28</v>
       </c>
       <c r="L57" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="M57" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N57" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="O57" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="P57" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="Q57" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="R57">
-        <v>712.06</v>
+        <v>165</v>
       </c>
       <c r="S57" t="s">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="T57" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="U57" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="V57">
-        <v>677.88</v>
+        <v>165</v>
       </c>
       <c r="W57" t="s">
         <v>228</v>
@@ -5234,19 +5327,19 @@
         <v>202</v>
       </c>
       <c r="E58" t="s">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="F58" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="G58" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H58" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="I58" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="J58" t="s">
         <v>27</v>
@@ -5255,40 +5348,43 @@
         <v>28</v>
       </c>
       <c r="L58" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M58" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="N58" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="O58" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="P58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="R58">
-        <v>3894.37</v>
+        <v>320</v>
       </c>
       <c r="S58" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="T58" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="U58" t="s">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="V58">
-        <v>3894.37</v>
+        <v>320</v>
       </c>
       <c r="W58" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X58" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.25">
@@ -5305,7 +5401,7 @@
         <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F59" t="s">
         <v>90</v>
@@ -5326,7 +5422,7 @@
         <v>28</v>
       </c>
       <c r="L59" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="M59" t="s">
         <v>54</v>
@@ -5338,31 +5434,31 @@
         <v>97</v>
       </c>
       <c r="P59" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="Q59" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="R59">
-        <v>956</v>
+        <v>3397</v>
       </c>
       <c r="S59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T59" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="U59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V59">
-        <v>956</v>
+        <v>3397</v>
       </c>
       <c r="W59" t="s">
         <v>214</v>
       </c>
       <c r="X59" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.25">
@@ -5379,7 +5475,7 @@
         <v>202</v>
       </c>
       <c r="E60" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F60" t="s">
         <v>90</v>
@@ -5394,16 +5490,16 @@
         <v>95</v>
       </c>
       <c r="J60" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="K60" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="L60" t="s">
-        <v>89</v>
+        <v>160</v>
       </c>
       <c r="M60" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="N60" t="s">
         <v>96</v>
@@ -5412,31 +5508,28 @@
         <v>97</v>
       </c>
       <c r="P60" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="Q60" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R60">
-        <v>2328</v>
+        <v>22827.24</v>
       </c>
       <c r="S60" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="T60" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="U60" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="V60">
-        <v>2328</v>
+        <v>22827.24</v>
       </c>
       <c r="W60" t="s">
-        <v>214</v>
-      </c>
-      <c r="X60" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.25">
@@ -5453,7 +5546,7 @@
         <v>202</v>
       </c>
       <c r="E61" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="F61" t="s">
         <v>90</v>
@@ -5474,7 +5567,7 @@
         <v>28</v>
       </c>
       <c r="L61" t="s">
-        <v>160</v>
+        <v>39</v>
       </c>
       <c r="M61" t="s">
         <v>54</v>
@@ -5486,25 +5579,25 @@
         <v>97</v>
       </c>
       <c r="P61" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="Q61" t="s">
         <v>39</v>
       </c>
       <c r="R61">
-        <v>22827.24</v>
+        <v>416</v>
       </c>
       <c r="S61" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="T61" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="U61" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="V61">
-        <v>22827.24</v>
+        <v>416</v>
       </c>
       <c r="W61" t="s">
         <v>228</v>
@@ -5524,7 +5617,7 @@
         <v>202</v>
       </c>
       <c r="E62" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F62" t="s">
         <v>90</v>
@@ -5545,7 +5638,7 @@
         <v>28</v>
       </c>
       <c r="L62" t="s">
-        <v>159</v>
+        <v>64</v>
       </c>
       <c r="M62" t="s">
         <v>54</v>
@@ -5557,25 +5650,25 @@
         <v>97</v>
       </c>
       <c r="P62" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="Q62" t="s">
         <v>39</v>
       </c>
       <c r="R62">
-        <v>5062</v>
+        <v>1912</v>
       </c>
       <c r="S62" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="T62" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="U62" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="V62">
-        <v>5062</v>
+        <v>1912</v>
       </c>
       <c r="W62" t="s">
         <v>228</v>
@@ -5595,7 +5688,7 @@
         <v>202</v>
       </c>
       <c r="E63" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F63" t="s">
         <v>90</v>
@@ -5604,10 +5697,10 @@
         <v>91</v>
       </c>
       <c r="H63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I63" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J63" t="s">
         <v>27</v>
@@ -5616,43 +5709,40 @@
         <v>28</v>
       </c>
       <c r="L63" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="M63" t="s">
         <v>54</v>
       </c>
       <c r="N63" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="O63" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="P63" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="Q63" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="R63">
-        <v>320</v>
+        <v>712.06</v>
       </c>
       <c r="S63" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="T63" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="U63" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="V63">
-        <v>320</v>
+        <v>677.88</v>
       </c>
       <c r="W63" t="s">
-        <v>214</v>
-      </c>
-      <c r="X63" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
@@ -5669,7 +5759,7 @@
         <v>202</v>
       </c>
       <c r="E64" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F64" t="s">
         <v>90</v>
@@ -5690,7 +5780,7 @@
         <v>28</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="M64" t="s">
         <v>54</v>
@@ -5702,31 +5792,28 @@
         <v>97</v>
       </c>
       <c r="P64" t="s">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="Q64" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="R64">
-        <v>3397</v>
+        <v>416</v>
       </c>
       <c r="S64" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="T64" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="U64" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="V64">
-        <v>3397</v>
+        <v>416</v>
       </c>
       <c r="W64" t="s">
-        <v>214</v>
-      </c>
-      <c r="X64" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.25">
@@ -5743,7 +5830,7 @@
         <v>202</v>
       </c>
       <c r="E65" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F65" t="s">
         <v>90</v>
@@ -5764,7 +5851,7 @@
         <v>28</v>
       </c>
       <c r="L65" t="s">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="M65" t="s">
         <v>54</v>
@@ -5776,25 +5863,25 @@
         <v>97</v>
       </c>
       <c r="P65" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="Q65" t="s">
         <v>39</v>
       </c>
       <c r="R65">
-        <v>162.84</v>
+        <v>596</v>
       </c>
       <c r="S65" t="s">
-        <v>199</v>
+        <v>134</v>
       </c>
       <c r="T65" t="s">
         <v>71</v>
       </c>
       <c r="U65" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="V65">
-        <v>162.84</v>
+        <v>596</v>
       </c>
       <c r="W65" t="s">
         <v>228</v>
@@ -5885,7 +5972,7 @@
         <v>202</v>
       </c>
       <c r="E67" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F67" t="s">
         <v>90</v>
@@ -5906,7 +5993,7 @@
         <v>28</v>
       </c>
       <c r="L67" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="M67" t="s">
         <v>54</v>
@@ -5924,19 +6011,19 @@
         <v>39</v>
       </c>
       <c r="R67">
-        <v>956</v>
+        <v>4554</v>
       </c>
       <c r="S67" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="T67" t="s">
         <v>71</v>
       </c>
       <c r="U67" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="V67">
-        <v>956</v>
+        <v>4554</v>
       </c>
       <c r="W67" t="s">
         <v>228</v>
@@ -5956,7 +6043,7 @@
         <v>202</v>
       </c>
       <c r="E68" t="s">
-        <v>166</v>
+        <v>205</v>
       </c>
       <c r="F68" t="s">
         <v>90</v>
@@ -5971,16 +6058,16 @@
         <v>95</v>
       </c>
       <c r="J68" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="K68" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="L68" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="M68" t="s">
-        <v>54</v>
+        <v>127</v>
       </c>
       <c r="N68" t="s">
         <v>96</v>
@@ -5995,19 +6082,19 @@
         <v>39</v>
       </c>
       <c r="R68">
-        <v>416</v>
+        <v>2328</v>
       </c>
       <c r="S68" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="T68" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="U68" t="s">
-        <v>112</v>
+        <v>206</v>
       </c>
       <c r="V68">
-        <v>416</v>
+        <v>2328</v>
       </c>
       <c r="W68" t="s">
         <v>228</v>
@@ -6027,7 +6114,7 @@
         <v>202</v>
       </c>
       <c r="E69" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F69" t="s">
         <v>90</v>
@@ -6036,10 +6123,10 @@
         <v>91</v>
       </c>
       <c r="H69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I69" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J69" t="s">
         <v>27</v>
@@ -6048,37 +6135,37 @@
         <v>28</v>
       </c>
       <c r="L69" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="M69" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N69" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="O69" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="P69" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="Q69" t="s">
         <v>39</v>
       </c>
       <c r="R69">
-        <v>596</v>
+        <v>6012.64</v>
       </c>
       <c r="S69" t="s">
-        <v>134</v>
+        <v>189</v>
       </c>
       <c r="T69" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="U69" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="V69">
-        <v>596</v>
+        <v>5724.03</v>
       </c>
       <c r="W69" t="s">
         <v>228</v>
@@ -6098,7 +6185,7 @@
         <v>202</v>
       </c>
       <c r="E70" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F70" t="s">
         <v>90</v>
@@ -6119,7 +6206,7 @@
         <v>28</v>
       </c>
       <c r="L70" t="s">
-        <v>66</v>
+        <v>159</v>
       </c>
       <c r="M70" t="s">
         <v>54</v>
@@ -6131,25 +6218,25 @@
         <v>97</v>
       </c>
       <c r="P70" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="Q70" t="s">
         <v>39</v>
       </c>
       <c r="R70">
-        <v>416</v>
+        <v>5062</v>
       </c>
       <c r="S70" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="T70" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="U70" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="V70">
-        <v>416</v>
+        <v>5062</v>
       </c>
       <c r="W70" t="s">
         <v>228</v>
@@ -6169,7 +6256,7 @@
         <v>202</v>
       </c>
       <c r="E71" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F71" t="s">
         <v>90</v>
@@ -6190,7 +6277,7 @@
         <v>28</v>
       </c>
       <c r="L71" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="M71" t="s">
         <v>54</v>
@@ -6202,25 +6289,25 @@
         <v>97</v>
       </c>
       <c r="P71" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="Q71" t="s">
         <v>39</v>
       </c>
       <c r="R71">
-        <v>4554</v>
+        <v>162.84</v>
       </c>
       <c r="S71" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="T71" t="s">
         <v>71</v>
       </c>
       <c r="U71" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="V71">
-        <v>4554</v>
+        <v>162.84</v>
       </c>
       <c r="W71" t="s">
         <v>228</v>
@@ -6240,7 +6327,7 @@
         <v>202</v>
       </c>
       <c r="E72" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F72" t="s">
         <v>90</v>
@@ -6261,7 +6348,7 @@
         <v>28</v>
       </c>
       <c r="L72" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M72" t="s">
         <v>54</v>
@@ -6279,19 +6366,19 @@
         <v>39</v>
       </c>
       <c r="R72">
-        <v>1912</v>
+        <v>956</v>
       </c>
       <c r="S72" t="s">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="T72" t="s">
         <v>71</v>
       </c>
       <c r="U72" t="s">
-        <v>112</v>
+        <v>200</v>
       </c>
       <c r="V72">
-        <v>1912</v>
+        <v>956</v>
       </c>
       <c r="W72" t="s">
         <v>228</v>
@@ -6311,64 +6398,1063 @@
         <v>202</v>
       </c>
       <c r="E73" t="s">
-        <v>205</v>
+        <v>166</v>
       </c>
       <c r="F73" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="I73" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="J73" t="s">
-        <v>156</v>
+        <v>27</v>
       </c>
       <c r="K73" t="s">
-        <v>157</v>
+        <v>28</v>
       </c>
       <c r="L73" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="M73" t="s">
-        <v>127</v>
+        <v>29</v>
       </c>
       <c r="N73" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="O73" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="P73" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="Q73" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="R73">
-        <v>2328</v>
+        <v>3894.37</v>
       </c>
       <c r="S73" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="T73" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U73" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="V73">
-        <v>2328</v>
+        <v>3894.37</v>
       </c>
       <c r="W73" t="s">
         <v>228</v>
       </c>
     </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>197</v>
+      </c>
+      <c r="C74" t="s">
+        <v>201</v>
+      </c>
+      <c r="D74" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" t="s">
+        <v>166</v>
+      </c>
+      <c r="F74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G74" t="s">
+        <v>73</v>
+      </c>
+      <c r="H74" t="s">
+        <v>39</v>
+      </c>
+      <c r="I74" t="s">
+        <v>80</v>
+      </c>
+      <c r="J74" t="s">
+        <v>27</v>
+      </c>
+      <c r="K74" t="s">
+        <v>28</v>
+      </c>
+      <c r="L74" t="s">
+        <v>170</v>
+      </c>
+      <c r="M74" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" t="s">
+        <v>74</v>
+      </c>
+      <c r="O74" t="s">
+        <v>75</v>
+      </c>
+      <c r="P74" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>34</v>
+      </c>
+      <c r="R74">
+        <v>58049.66</v>
+      </c>
+      <c r="S74" t="s">
+        <v>229</v>
+      </c>
+      <c r="T74" t="s">
+        <v>230</v>
+      </c>
+      <c r="U74" t="s">
+        <v>231</v>
+      </c>
+      <c r="V74">
+        <v>47980.55</v>
+      </c>
+      <c r="W74" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>197</v>
+      </c>
+      <c r="C75" t="s">
+        <v>201</v>
+      </c>
+      <c r="D75" t="s">
+        <v>202</v>
+      </c>
+      <c r="E75" t="s">
+        <v>166</v>
+      </c>
+      <c r="F75" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" t="s">
+        <v>232</v>
+      </c>
+      <c r="H75" t="s">
+        <v>233</v>
+      </c>
+      <c r="I75" t="s">
+        <v>234</v>
+      </c>
+      <c r="J75" t="s">
+        <v>27</v>
+      </c>
+      <c r="K75" t="s">
+        <v>28</v>
+      </c>
+      <c r="L75" t="s">
+        <v>235</v>
+      </c>
+      <c r="M75" t="s">
+        <v>88</v>
+      </c>
+      <c r="N75" t="s">
+        <v>236</v>
+      </c>
+      <c r="O75" t="s">
+        <v>237</v>
+      </c>
+      <c r="P75" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>30</v>
+      </c>
+      <c r="R75">
+        <v>5866.75</v>
+      </c>
+      <c r="S75" t="s">
+        <v>239</v>
+      </c>
+      <c r="T75" t="s">
+        <v>240</v>
+      </c>
+      <c r="U75" t="s">
+        <v>241</v>
+      </c>
+      <c r="V75">
+        <v>5852.67</v>
+      </c>
+      <c r="W75" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" t="s">
+        <v>201</v>
+      </c>
+      <c r="D76" t="s">
+        <v>202</v>
+      </c>
+      <c r="E76" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" t="s">
+        <v>90</v>
+      </c>
+      <c r="G76" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76" t="s">
+        <v>35</v>
+      </c>
+      <c r="I76" t="s">
+        <v>95</v>
+      </c>
+      <c r="J76" t="s">
+        <v>27</v>
+      </c>
+      <c r="K76" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" t="s">
+        <v>39</v>
+      </c>
+      <c r="M76" t="s">
+        <v>54</v>
+      </c>
+      <c r="N76" t="s">
+        <v>96</v>
+      </c>
+      <c r="O76" t="s">
+        <v>97</v>
+      </c>
+      <c r="P76" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>59</v>
+      </c>
+      <c r="R76">
+        <v>416</v>
+      </c>
+      <c r="S76" t="s">
+        <v>243</v>
+      </c>
+      <c r="T76" t="s">
+        <v>240</v>
+      </c>
+      <c r="U76" t="s">
+        <v>241</v>
+      </c>
+      <c r="V76">
+        <v>416</v>
+      </c>
+      <c r="W76" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>197</v>
+      </c>
+      <c r="C77" t="s">
+        <v>201</v>
+      </c>
+      <c r="D77" t="s">
+        <v>202</v>
+      </c>
+      <c r="E77" t="s">
+        <v>204</v>
+      </c>
+      <c r="F77" t="s">
+        <v>90</v>
+      </c>
+      <c r="G77" t="s">
+        <v>91</v>
+      </c>
+      <c r="H77" t="s">
+        <v>35</v>
+      </c>
+      <c r="I77" t="s">
+        <v>95</v>
+      </c>
+      <c r="J77" t="s">
+        <v>27</v>
+      </c>
+      <c r="K77" t="s">
+        <v>28</v>
+      </c>
+      <c r="L77" t="s">
+        <v>160</v>
+      </c>
+      <c r="M77" t="s">
+        <v>54</v>
+      </c>
+      <c r="N77" t="s">
+        <v>96</v>
+      </c>
+      <c r="O77" t="s">
+        <v>97</v>
+      </c>
+      <c r="P77" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>59</v>
+      </c>
+      <c r="R77">
+        <v>22827.24</v>
+      </c>
+      <c r="S77" t="s">
+        <v>244</v>
+      </c>
+      <c r="T77" t="s">
+        <v>240</v>
+      </c>
+      <c r="U77" t="s">
+        <v>241</v>
+      </c>
+      <c r="V77">
+        <v>22827.24</v>
+      </c>
+      <c r="W77" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>197</v>
+      </c>
+      <c r="C78" t="s">
+        <v>201</v>
+      </c>
+      <c r="D78" t="s">
+        <v>202</v>
+      </c>
+      <c r="E78" t="s">
+        <v>204</v>
+      </c>
+      <c r="F78" t="s">
+        <v>90</v>
+      </c>
+      <c r="G78" t="s">
+        <v>91</v>
+      </c>
+      <c r="H78" t="s">
+        <v>35</v>
+      </c>
+      <c r="I78" t="s">
+        <v>95</v>
+      </c>
+      <c r="J78" t="s">
+        <v>27</v>
+      </c>
+      <c r="K78" t="s">
+        <v>28</v>
+      </c>
+      <c r="L78" t="s">
+        <v>64</v>
+      </c>
+      <c r="M78" t="s">
+        <v>54</v>
+      </c>
+      <c r="N78" t="s">
+        <v>96</v>
+      </c>
+      <c r="O78" t="s">
+        <v>97</v>
+      </c>
+      <c r="P78" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>59</v>
+      </c>
+      <c r="R78">
+        <v>1912</v>
+      </c>
+      <c r="S78" t="s">
+        <v>245</v>
+      </c>
+      <c r="T78" t="s">
+        <v>240</v>
+      </c>
+      <c r="U78" t="s">
+        <v>241</v>
+      </c>
+      <c r="V78">
+        <v>1912</v>
+      </c>
+      <c r="W78" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>197</v>
+      </c>
+      <c r="C79" t="s">
+        <v>201</v>
+      </c>
+      <c r="D79" t="s">
+        <v>202</v>
+      </c>
+      <c r="E79" t="s">
+        <v>207</v>
+      </c>
+      <c r="F79" t="s">
+        <v>90</v>
+      </c>
+      <c r="G79" t="s">
+        <v>91</v>
+      </c>
+      <c r="H79" t="s">
+        <v>35</v>
+      </c>
+      <c r="I79" t="s">
+        <v>95</v>
+      </c>
+      <c r="J79" t="s">
+        <v>27</v>
+      </c>
+      <c r="K79" t="s">
+        <v>28</v>
+      </c>
+      <c r="L79" t="s">
+        <v>159</v>
+      </c>
+      <c r="M79" t="s">
+        <v>54</v>
+      </c>
+      <c r="N79" t="s">
+        <v>96</v>
+      </c>
+      <c r="O79" t="s">
+        <v>97</v>
+      </c>
+      <c r="P79" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>59</v>
+      </c>
+      <c r="R79">
+        <v>5062</v>
+      </c>
+      <c r="S79" t="s">
+        <v>246</v>
+      </c>
+      <c r="T79" t="s">
+        <v>240</v>
+      </c>
+      <c r="U79" t="s">
+        <v>241</v>
+      </c>
+      <c r="V79">
+        <v>5062</v>
+      </c>
+      <c r="W79" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>197</v>
+      </c>
+      <c r="C80" t="s">
+        <v>201</v>
+      </c>
+      <c r="D80" t="s">
+        <v>202</v>
+      </c>
+      <c r="E80" t="s">
+        <v>207</v>
+      </c>
+      <c r="F80" t="s">
+        <v>90</v>
+      </c>
+      <c r="G80" t="s">
+        <v>91</v>
+      </c>
+      <c r="H80" t="s">
+        <v>35</v>
+      </c>
+      <c r="I80" t="s">
+        <v>95</v>
+      </c>
+      <c r="J80" t="s">
+        <v>27</v>
+      </c>
+      <c r="K80" t="s">
+        <v>28</v>
+      </c>
+      <c r="L80" t="s">
+        <v>59</v>
+      </c>
+      <c r="M80" t="s">
+        <v>54</v>
+      </c>
+      <c r="N80" t="s">
+        <v>96</v>
+      </c>
+      <c r="O80" t="s">
+        <v>97</v>
+      </c>
+      <c r="P80" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>59</v>
+      </c>
+      <c r="R80">
+        <v>956</v>
+      </c>
+      <c r="S80" t="s">
+        <v>247</v>
+      </c>
+      <c r="T80" t="s">
+        <v>240</v>
+      </c>
+      <c r="U80" t="s">
+        <v>241</v>
+      </c>
+      <c r="V80">
+        <v>956</v>
+      </c>
+      <c r="W80" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>197</v>
+      </c>
+      <c r="C81" t="s">
+        <v>201</v>
+      </c>
+      <c r="D81" t="s">
+        <v>202</v>
+      </c>
+      <c r="E81" t="s">
+        <v>208</v>
+      </c>
+      <c r="F81" t="s">
+        <v>90</v>
+      </c>
+      <c r="G81" t="s">
+        <v>91</v>
+      </c>
+      <c r="H81" t="s">
+        <v>35</v>
+      </c>
+      <c r="I81" t="s">
+        <v>95</v>
+      </c>
+      <c r="J81" t="s">
+        <v>27</v>
+      </c>
+      <c r="K81" t="s">
+        <v>28</v>
+      </c>
+      <c r="L81" t="s">
+        <v>66</v>
+      </c>
+      <c r="M81" t="s">
+        <v>54</v>
+      </c>
+      <c r="N81" t="s">
+        <v>96</v>
+      </c>
+      <c r="O81" t="s">
+        <v>97</v>
+      </c>
+      <c r="P81" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>59</v>
+      </c>
+      <c r="R81">
+        <v>416</v>
+      </c>
+      <c r="S81" t="s">
+        <v>248</v>
+      </c>
+      <c r="T81" t="s">
+        <v>240</v>
+      </c>
+      <c r="U81" t="s">
+        <v>241</v>
+      </c>
+      <c r="V81">
+        <v>416</v>
+      </c>
+      <c r="W81" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>197</v>
+      </c>
+      <c r="C82" t="s">
+        <v>201</v>
+      </c>
+      <c r="D82" t="s">
+        <v>202</v>
+      </c>
+      <c r="E82" t="s">
+        <v>209</v>
+      </c>
+      <c r="F82" t="s">
+        <v>90</v>
+      </c>
+      <c r="G82" t="s">
+        <v>91</v>
+      </c>
+      <c r="H82" t="s">
+        <v>35</v>
+      </c>
+      <c r="I82" t="s">
+        <v>95</v>
+      </c>
+      <c r="J82" t="s">
+        <v>27</v>
+      </c>
+      <c r="K82" t="s">
+        <v>28</v>
+      </c>
+      <c r="L82" t="s">
+        <v>101</v>
+      </c>
+      <c r="M82" t="s">
+        <v>54</v>
+      </c>
+      <c r="N82" t="s">
+        <v>96</v>
+      </c>
+      <c r="O82" t="s">
+        <v>97</v>
+      </c>
+      <c r="P82" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>59</v>
+      </c>
+      <c r="R82">
+        <v>596</v>
+      </c>
+      <c r="S82" t="s">
+        <v>249</v>
+      </c>
+      <c r="T82" t="s">
+        <v>240</v>
+      </c>
+      <c r="U82" t="s">
+        <v>241</v>
+      </c>
+      <c r="V82">
+        <v>596</v>
+      </c>
+      <c r="W82" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>197</v>
+      </c>
+      <c r="C83" t="s">
+        <v>201</v>
+      </c>
+      <c r="D83" t="s">
+        <v>202</v>
+      </c>
+      <c r="E83" t="s">
+        <v>210</v>
+      </c>
+      <c r="F83" t="s">
+        <v>90</v>
+      </c>
+      <c r="G83" t="s">
+        <v>91</v>
+      </c>
+      <c r="H83" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83" t="s">
+        <v>95</v>
+      </c>
+      <c r="J83" t="s">
+        <v>27</v>
+      </c>
+      <c r="K83" t="s">
+        <v>28</v>
+      </c>
+      <c r="L83" t="s">
+        <v>182</v>
+      </c>
+      <c r="M83" t="s">
+        <v>54</v>
+      </c>
+      <c r="N83" t="s">
+        <v>96</v>
+      </c>
+      <c r="O83" t="s">
+        <v>97</v>
+      </c>
+      <c r="P83" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>59</v>
+      </c>
+      <c r="R83">
+        <v>1225</v>
+      </c>
+      <c r="S83" t="s">
+        <v>250</v>
+      </c>
+      <c r="T83" t="s">
+        <v>240</v>
+      </c>
+      <c r="U83" t="s">
+        <v>241</v>
+      </c>
+      <c r="V83">
+        <v>1225</v>
+      </c>
+      <c r="W83" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>197</v>
+      </c>
+      <c r="C84" t="s">
+        <v>201</v>
+      </c>
+      <c r="D84" t="s">
+        <v>202</v>
+      </c>
+      <c r="E84" t="s">
+        <v>210</v>
+      </c>
+      <c r="F84" t="s">
+        <v>90</v>
+      </c>
+      <c r="G84" t="s">
+        <v>91</v>
+      </c>
+      <c r="H84" t="s">
+        <v>35</v>
+      </c>
+      <c r="I84" t="s">
+        <v>95</v>
+      </c>
+      <c r="J84" t="s">
+        <v>27</v>
+      </c>
+      <c r="K84" t="s">
+        <v>28</v>
+      </c>
+      <c r="L84" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" t="s">
+        <v>54</v>
+      </c>
+      <c r="N84" t="s">
+        <v>96</v>
+      </c>
+      <c r="O84" t="s">
+        <v>97</v>
+      </c>
+      <c r="P84" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>64</v>
+      </c>
+      <c r="R84">
+        <v>3397</v>
+      </c>
+      <c r="S84" t="s">
+        <v>251</v>
+      </c>
+      <c r="T84" t="s">
+        <v>240</v>
+      </c>
+      <c r="U84" t="s">
+        <v>241</v>
+      </c>
+      <c r="V84">
+        <v>3397</v>
+      </c>
+      <c r="W84" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>197</v>
+      </c>
+      <c r="C85" t="s">
+        <v>201</v>
+      </c>
+      <c r="D85" t="s">
+        <v>202</v>
+      </c>
+      <c r="E85" t="s">
+        <v>210</v>
+      </c>
+      <c r="F85" t="s">
+        <v>90</v>
+      </c>
+      <c r="G85" t="s">
+        <v>91</v>
+      </c>
+      <c r="H85" t="s">
+        <v>35</v>
+      </c>
+      <c r="I85" t="s">
+        <v>95</v>
+      </c>
+      <c r="J85" t="s">
+        <v>27</v>
+      </c>
+      <c r="K85" t="s">
+        <v>28</v>
+      </c>
+      <c r="L85" t="s">
+        <v>26</v>
+      </c>
+      <c r="M85" t="s">
+        <v>54</v>
+      </c>
+      <c r="N85" t="s">
+        <v>96</v>
+      </c>
+      <c r="O85" t="s">
+        <v>97</v>
+      </c>
+      <c r="P85" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>27</v>
+      </c>
+      <c r="R85">
+        <v>320</v>
+      </c>
+      <c r="S85" t="s">
+        <v>252</v>
+      </c>
+      <c r="T85" t="s">
+        <v>240</v>
+      </c>
+      <c r="U85" t="s">
+        <v>241</v>
+      </c>
+      <c r="V85">
+        <v>320</v>
+      </c>
+      <c r="W85" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>197</v>
+      </c>
+      <c r="C86" t="s">
+        <v>201</v>
+      </c>
+      <c r="D86" t="s">
+        <v>202</v>
+      </c>
+      <c r="E86" t="s">
+        <v>205</v>
+      </c>
+      <c r="F86" t="s">
+        <v>90</v>
+      </c>
+      <c r="G86" t="s">
+        <v>91</v>
+      </c>
+      <c r="H86" t="s">
+        <v>35</v>
+      </c>
+      <c r="I86" t="s">
+        <v>95</v>
+      </c>
+      <c r="J86" t="s">
+        <v>156</v>
+      </c>
+      <c r="K86" t="s">
+        <v>157</v>
+      </c>
+      <c r="L86" t="s">
+        <v>89</v>
+      </c>
+      <c r="M86" t="s">
+        <v>127</v>
+      </c>
+      <c r="N86" t="s">
+        <v>96</v>
+      </c>
+      <c r="O86" t="s">
+        <v>97</v>
+      </c>
+      <c r="P86" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>59</v>
+      </c>
+      <c r="R86">
+        <v>6972</v>
+      </c>
+      <c r="S86" t="s">
+        <v>253</v>
+      </c>
+      <c r="T86" t="s">
+        <v>254</v>
+      </c>
+      <c r="U86" t="s">
+        <v>255</v>
+      </c>
+      <c r="V86">
+        <v>6972</v>
+      </c>
+      <c r="W86" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" t="s">
+        <v>201</v>
+      </c>
+      <c r="D87" t="s">
+        <v>202</v>
+      </c>
+      <c r="E87" t="s">
+        <v>207</v>
+      </c>
+      <c r="F87" t="s">
+        <v>90</v>
+      </c>
+      <c r="G87" t="s">
+        <v>91</v>
+      </c>
+      <c r="H87" t="s">
+        <v>35</v>
+      </c>
+      <c r="I87" t="s">
+        <v>95</v>
+      </c>
+      <c r="J87" t="s">
+        <v>27</v>
+      </c>
+      <c r="K87" t="s">
+        <v>28</v>
+      </c>
+      <c r="L87" t="s">
+        <v>158</v>
+      </c>
+      <c r="M87" t="s">
+        <v>54</v>
+      </c>
+      <c r="N87" t="s">
+        <v>96</v>
+      </c>
+      <c r="O87" t="s">
+        <v>97</v>
+      </c>
+      <c r="P87" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>59</v>
+      </c>
+      <c r="R87">
+        <v>539.58000000000004</v>
+      </c>
+      <c r="S87" t="s">
+        <v>256</v>
+      </c>
+      <c r="T87" t="s">
+        <v>240</v>
+      </c>
+      <c r="U87" t="s">
+        <v>255</v>
+      </c>
+      <c r="V87">
+        <v>539.58000000000004</v>
+      </c>
+      <c r="W87" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:Y1">
+    <sortState ref="A2:Y73">
+      <sortCondition ref="U1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/upload/pagamentos2026.xlsx
+++ b/upload/pagamentos2026.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1873" uniqueCount="260">
   <si>
     <t>ano</t>
   </si>
@@ -793,6 +793,15 @@
   </si>
   <si>
     <t>254</t>
+  </si>
+  <si>
+    <t>O pagamento foi realizado em 08/06/2026 em razão da limitação financeira disponível. Diante da necessidade de quitação de obrigações prioritárias já vencidas, o pagamento desta despesa ocorreu posteriormente.</t>
+  </si>
+  <si>
+    <t>O pagamento foi realizado em 26/06/2026, em vez de 12/07/2026, data do vencimento do boleto, em decorrência de falha operacional ocorrida no processamento da despesa.</t>
+  </si>
+  <si>
+    <t>O pagamento foi realizado em 30/06/2026 em razão da limitação financeira disponível. Diante da necessidade de quitação de obrigações prioritárias já vencidas, o pagamento desta despesa ocorreu posteriormente.</t>
   </si>
 </sst>
 </file>
@@ -1157,6 +1166,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="14" max="14" width="80" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -3336,7 +3348,10 @@
         <v>125.76</v>
       </c>
       <c r="W30" t="s">
-        <v>228</v>
+        <v>214</v>
+      </c>
+      <c r="X30" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.25">
@@ -5816,7 +5831,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -5887,7 +5902,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -5958,7 +5973,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -6029,7 +6044,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -6100,7 +6115,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -6171,7 +6186,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -6239,10 +6254,13 @@
         <v>5062</v>
       </c>
       <c r="W70" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="X70" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -6310,10 +6328,13 @@
         <v>162.84</v>
       </c>
       <c r="W71" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="X71" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -6381,10 +6402,13 @@
         <v>956</v>
       </c>
       <c r="W72" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="X72" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -6455,7 +6479,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -6526,7 +6550,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -6594,10 +6618,13 @@
         <v>5852.67</v>
       </c>
       <c r="W75" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="X75" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -6668,7 +6695,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -6739,7 +6766,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>25</v>
       </c>
@@ -6810,7 +6837,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>25</v>
       </c>
@@ -6881,7 +6908,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -6952,7 +6979,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -7023,7 +7050,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -7094,7 +7121,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -7165,7 +7192,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -7236,7 +7263,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -7307,7 +7334,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -7375,10 +7402,13 @@
         <v>6972</v>
       </c>
       <c r="W86" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="X86" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
